--- a/artfynd/A 5978-2024 artfynd.xlsx
+++ b/artfynd/A 5978-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5978-2024 artfynd.xlsx
+++ b/artfynd/A 5978-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67522033</v>
+        <v>67521935</v>
       </c>
       <c r="B2" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406683.6007598815</v>
+        <v>406698</v>
       </c>
       <c r="R2" t="n">
-        <v>6632147.682025457</v>
+        <v>6632226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,24 +753,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på sten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,12 +785,7 @@
         <v>67521966</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406674.4228637309</v>
+        <v>406674</v>
       </c>
       <c r="R3" t="n">
-        <v>6632183.638602205</v>
+        <v>6632184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +860,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67521935</v>
+        <v>67521979</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406697.6597912354</v>
+        <v>406714</v>
       </c>
       <c r="R4" t="n">
-        <v>6632225.825347343</v>
+        <v>6632237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,19 +967,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,16 +999,11 @@
         <v>67522010</v>
       </c>
       <c r="B5" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1096,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406700.4131121339</v>
+        <v>406700</v>
       </c>
       <c r="R5" t="n">
-        <v>6632154.8076915</v>
+        <v>6632155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,19 +1074,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1170,6 +1105,118 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>67522033</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lipen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>406684</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6632148</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på sten</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
